--- a/data/trans_bre/P57_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P57_R-Estudios-trans_bre.xlsx
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,58; 13,3</t>
+          <t>4,28; 13,18</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,48; 11,49</t>
+          <t>2,33; 11,43</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>13,84; 48,11</t>
+          <t>12,96; 47,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,48; 42,54</t>
+          <t>7,05; 42,88</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 5,95</t>
+          <t>0,77; 5,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 4,8</t>
+          <t>-1,83; 4,59</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5,23; 39,94</t>
+          <t>4,44; 38,79</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-17,77; 61,04</t>
+          <t>-16,09; 59,06</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,09; 1,41</t>
+          <t>-5,91; 1,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 2,35</t>
+          <t>-3,44; 2,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-45,71; 16,29</t>
+          <t>-44,09; 18,61</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-32,62; 35,98</t>
+          <t>-33,56; 32,16</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,85; 6,79</t>
+          <t>2,87; 7,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 5,86</t>
+          <t>0,44; 6,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>14,76; 38,86</t>
+          <t>15,19; 39,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,61; 55,4</t>
+          <t>3,68; 58,85</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P57_R-Estudios-trans_bre.xlsx
+++ b/data/trans_bre/P57_R-Estudios-trans_bre.xlsx
@@ -578,7 +578,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>8,29</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>29,3%</t>
         </is>
       </c>
     </row>
@@ -601,22 +601,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,28; 13,18</t>
+          <t>3,86; 12,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 11,43</t>
+          <t>3,84; 12,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,96; 47,18</t>
+          <t>12,29; 46,89</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7,05; 42,88</t>
+          <t>12,74; 50,24</t>
         </is>
       </c>
     </row>
@@ -638,7 +638,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,24</t>
+          <t>2,04</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -648,7 +648,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>18,48%</t>
         </is>
       </c>
     </row>
@@ -661,22 +661,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,85</t>
+          <t>0,84; 5,76</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-1,83; 4,59</t>
+          <t>0,13; 3,88</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,44; 38,79</t>
+          <t>4,68; 38,03</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-16,09; 59,06</t>
+          <t>1,14; 39,37</t>
         </is>
       </c>
     </row>
@@ -698,7 +698,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>-0,56</t>
+          <t>-0,58</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-6,28%</t>
+          <t>-6,41%</t>
         </is>
       </c>
     </row>
@@ -721,22 +721,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,91; 1,52</t>
+          <t>-5,9; 1,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-3,44; 2,32</t>
+          <t>-3,5; 2,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-44,09; 18,61</t>
+          <t>-46,89; 16,05</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-33,56; 32,16</t>
+          <t>-32,98; 37,77</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3,23</t>
+          <t>3,86</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>28,79%</t>
         </is>
       </c>
     </row>
@@ -781,22 +781,22 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,87; 7,01</t>
+          <t>2,69; 6,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,44; 6,21</t>
+          <t>2,38; 5,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,19; 39,94</t>
+          <t>13,86; 39,46</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,68; 58,85</t>
+          <t>16,21; 41,56</t>
         </is>
       </c>
     </row>
